--- a/tests/workbooktests/workbooks/test_stochasticprocess.xlsx
+++ b/tests/workbooktests/workbooks/test_stochasticprocess.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3873556E-5085-49C1-912A-F3DCB2CC8E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B804ED3F-7F6A-4DEA-B5E6-17B0C0E8CCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7776" yWindow="1860" windowWidth="23040" windowHeight="14796" activeTab="2" xr2:uid="{536DAD22-F64C-4E0C-9C73-53C6A08A9B53}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" activeTab="2" xr2:uid="{536DAD22-F64C-4E0C-9C73-53C6A08A9B53}"/>
   </bookViews>
   <sheets>
     <sheet name="qlStochasticProcess(1D)" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -924,93 +924,90 @@
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" t="str" cm="1">
-        <f t="array" ref="B8">_xll.qlGeometricBrownianMotionProcess(B1,B2,B3)</f>
-        <v>⚡[test_stochasticprocess.xlsx]qlStochasticProcess(1D)!R8C2GeometricBrownianMotionProcess,A</v>
+      <c r="B8" t="e" cm="1">
+        <f t="array" aca="1" ref="B8" ca="1">_xll.qlGeometricBrownianMotionProcess(B1,B2,B3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B9" t="str" cm="1">
-        <f t="array" ref="B9">_xll.qlGeometricBrownianMotionProcess(B1,B2,B3)</f>
-        <v>⚡[test_stochasticprocess.xlsx]qlStochasticProcess(1D)!R9C2GeometricBrownianMotionProcess,A</v>
+      <c r="B9" t="e" cm="1">
+        <f t="array" aca="1" ref="B9" ca="1">_xll.qlGeometricBrownianMotionProcess(B1,B2,B3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
-      <c r="B11" t="str" cm="1">
-        <f t="array" ref="B11">_xll.qlStochasticProcessArray(B8,B5)</f>
-        <v>⚡[test_stochasticprocess.xlsx]qlStochasticProcess(1D)!R11C2StochasticProcessArray,A</v>
+      <c r="B11" t="e" cm="1">
+        <f t="array" aca="1" ref="B11" ca="1">_xll.qlStochasticProcessArray(B8,B5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
-      <c r="B12" t="str" cm="1">
-        <f t="array" ref="B12">_xll.qlStochasticProcessArray(B8:B9,B5:C6)</f>
-        <v>⚡[test_stochasticprocess.xlsx]qlStochasticProcess(1D)!R12C2StochasticProcessArray,A</v>
+      <c r="B12" t="e" cm="1">
+        <f t="array" aca="1" ref="B12" ca="1">_xll.qlStochasticProcessArray(B8:B9,B5:C6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
-      <c r="B14" cm="1">
-        <f t="array" ref="B14">_xll.qlStochasticProcessSize(B8)</f>
-        <v>1</v>
+      <c r="B14" t="e" cm="1">
+        <f t="array" aca="1" ref="B14" ca="1">_xll.qlStochasticProcessSize(B8)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
-      <c r="B15" cm="1">
-        <f t="array" ref="B15">_xll.qlStochasticProcessSize(B12)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B15" t="e" cm="1">
+        <f t="array" aca="1" ref="B15" ca="1">_xll.qlStochasticProcessSize(B12)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>7</v>
       </c>
-      <c r="B17" cm="1">
-        <f t="array" ref="B17">_xll.qlStochasticProcessFactors(B8)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B17" t="e" cm="1">
+        <f t="array" aca="1" ref="B17" ca="1">_xll.qlStochasticProcessFactors(B8)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>7</v>
       </c>
-      <c r="B18" cm="1">
-        <f t="array" ref="B18">_xll.qlStochasticProcessFactors(B12)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B18" t="e" cm="1">
+        <f t="array" aca="1" ref="B18" ca="1">_xll.qlStochasticProcessFactors(B12)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>8</v>
       </c>
-      <c r="B20" cm="1">
-        <f t="array" ref="B20">_xll.qlStochasticProcessInitialValues(B8)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B20" t="e" cm="1">
+        <f t="array" aca="1" ref="B20" ca="1">_xll.qlStochasticProcessInitialValues(B8)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>8</v>
       </c>
-      <c r="B21" cm="1">
-        <f t="array" ref="B21:C21">TRANSPOSE(_xll.qlStochasticProcessInitialValues(B12))</f>
-        <v>100</v>
-      </c>
-      <c r="C21">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B21" t="e" cm="1">
+        <f t="array" aca="1" ref="B21" ca="1">TRANSPOSE(_xll.qlStochasticProcessInitialValues(B12))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -1018,7 +1015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -1027,242 +1024,199 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>9</v>
       </c>
-      <c r="B26" cm="1">
-        <f t="array" ref="B26">_xll.qlStochasticProcessDrift(B11,B23,B24)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B26" t="e" cm="1">
+        <f t="array" aca="1" ref="B26" ca="1">_xll.qlStochasticProcessDrift(B11,B23,B24)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>9</v>
       </c>
-      <c r="B27" cm="1">
-        <f t="array" ref="B27:C27">TRANSPOSE(_xll.qlStochasticProcessDrift(B12,B23,_xlfn.ANCHORARRAY(B21)))</f>
-        <v>5</v>
-      </c>
-      <c r="C27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B27" t="e" cm="1">
+        <f t="array" aca="1" ref="B27" ca="1">TRANSPOSE(_xll.qlStochasticProcessDrift(B12,B23,_xlfn.ANCHORARRAY(B21)))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>12</v>
       </c>
-      <c r="B29" cm="1">
-        <f t="array" ref="B29">_xll.qlStochasticProcessDiffusion(B11,B23,B20)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B29" t="e" cm="1">
+        <f t="array" aca="1" ref="B29" ca="1">_xll.qlStochasticProcessDiffusion(B11,B23,B20)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>12</v>
       </c>
-      <c r="B30" cm="1">
-        <f t="array" ref="B30:C31">_xll.qlStochasticProcessDiffusion(B12,B23,_xlfn.ANCHORARRAY(B21))</f>
-        <v>15.491933384829666</v>
-      </c>
-      <c r="C30">
-        <v>12.649110640673518</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B31">
-        <v>15.491933384829668</v>
-      </c>
-      <c r="C31">
-        <v>-12.649110640673516</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B30" t="e" cm="1">
+        <f t="array" aca="1" ref="B30" ca="1">_xll.qlStochasticProcessDiffusion(B12,B23,_xlfn.ANCHORARRAY(B21))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>13</v>
       </c>
-      <c r="B33" cm="1">
-        <f t="array" ref="B33">_xll.qlStochasticProcessExpectation(B11,0,B20,B23)</f>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B33" t="e" cm="1">
+        <f t="array" aca="1" ref="B33" ca="1">_xll.qlStochasticProcessExpectation(B11,0,B20,B23)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>13</v>
       </c>
-      <c r="B34" cm="1">
-        <f t="array" ref="B34:C34">TRANSPOSE(_xll.qlStochasticProcessExpectation(B12,0,_xlfn.ANCHORARRAY(B21),B23))</f>
-        <v>110</v>
-      </c>
-      <c r="C34">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B34" t="e" cm="1">
+        <f t="array" aca="1" ref="B34" ca="1">TRANSPOSE(_xll.qlStochasticProcessExpectation(B12,0,_xlfn.ANCHORARRAY(B21),B23))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>14</v>
       </c>
-      <c r="B36" cm="1">
-        <f t="array" ref="B36">_xll.qlStochasticProcessStdDeviation(B11,0,B20,B23)</f>
-        <v>28.284271247461902</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B36" t="e" cm="1">
+        <f t="array" aca="1" ref="B36" ca="1">_xll.qlStochasticProcessStdDeviation(B11,0,B20,B23)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>14</v>
       </c>
-      <c r="B37" cm="1">
-        <f t="array" ref="B37:C38">_xll.qlStochasticProcessStdDeviation(B12,0,_xlfn.ANCHORARRAY(B21),B23)</f>
-        <v>21.908902300206645</v>
-      </c>
-      <c r="C37">
-        <v>17.888543819998318</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B38">
-        <v>21.908902300206645</v>
-      </c>
-      <c r="C38">
-        <v>-17.888543819998315</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B37" t="e" cm="1">
+        <f t="array" aca="1" ref="B37" ca="1">_xll.qlStochasticProcessStdDeviation(B12,0,_xlfn.ANCHORARRAY(B21),B23)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>15</v>
       </c>
-      <c r="B40" cm="1">
-        <f t="array" ref="B40">_xll.qlStochasticProcessCovariance(B11,0,B20,B23)</f>
-        <v>800.00000000000011</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B40" t="e" cm="1">
+        <f t="array" aca="1" ref="B40" ca="1">_xll.qlStochasticProcessCovariance(B11,0,B20,B23)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>15</v>
       </c>
-      <c r="B41" cm="1">
-        <f t="array" ref="B41:C42">_xll.qlStochasticProcessCovariance(B12,0,_xlfn.ANCHORARRAY(B21),B23)</f>
-        <v>800</v>
-      </c>
-      <c r="C41">
-        <v>160.00000000000006</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B42">
-        <v>160.00000000000006</v>
-      </c>
-      <c r="C42">
-        <v>799.99999999999989</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B41" t="e" cm="1">
+        <f t="array" aca="1" ref="B41" ca="1">_xll.qlStochasticProcessCovariance(B12,0,_xlfn.ANCHORARRAY(B21),B23)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>16</v>
       </c>
       <c r="B44">
         <f ca="1">2*(RAND()-0.5)</f>
-        <v>-0.21569842192469024</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.6926657892061725</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B45">
         <f ca="1">2*(RAND()-0.5)</f>
-        <v>0.74942782227420213</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.86808509225713104</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>17</v>
       </c>
-      <c r="B47" cm="1">
+      <c r="B47" t="e" cm="1">
         <f t="array" aca="1" ref="B47" ca="1">_xll.qlStochasticProcessEvolve(B11,0,B20,B23,B44)</f>
-        <v>103.89912732663258</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>17</v>
       </c>
-      <c r="B48" cm="1">
-        <f t="array" aca="1" ref="B48:C48" ca="1">TRANSPOSE(_xll.qlStochasticProcessEvolve(B12,0,_xlfn.ANCHORARRAY(B21),B23,B44:B45))</f>
-        <v>118.68045678642119</v>
-      </c>
-      <c r="C48">
-        <f ca="1"/>
-        <v>91.868111909065234</v>
+      <c r="B48" t="e" cm="1">
+        <f t="array" aca="1" ref="B48" ca="1">TRANSPOSE(_xll.qlStochasticProcessEvolve(B12,0,_xlfn.ANCHORARRAY(B21),B23,B44:B45))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
-      <c r="B51" cm="1">
-        <f t="array" ref="B51">_xll.qlStochasticProcess1DX0(B8)</f>
-        <v>100</v>
+      <c r="B51" t="e" cm="1">
+        <f t="array" aca="1" ref="B51" ca="1">_xll.qlStochasticProcess1DX0(B8)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>19</v>
       </c>
-      <c r="B52" cm="1">
-        <f t="array" ref="B52">_xll.qlStochasticProcess1DDrift(B8,B23,B24)</f>
-        <v>5</v>
+      <c r="B52" t="e" cm="1">
+        <f t="array" aca="1" ref="B52" ca="1">_xll.qlStochasticProcess1DDrift(B8,B23,B24)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>20</v>
       </c>
-      <c r="B53" cm="1">
-        <f t="array" ref="B53">_xll.qlStochasticProcess1DDiffusion(B8,B23,B24)</f>
-        <v>20</v>
+      <c r="B53" t="e" cm="1">
+        <f t="array" aca="1" ref="B53" ca="1">_xll.qlStochasticProcess1DDiffusion(B8,B23,B24)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>21</v>
       </c>
-      <c r="B54" cm="1">
-        <f t="array" ref="B54">_xll.qlStochasticProcess1DExpectation(B8,0,B20,B23)</f>
-        <v>110</v>
+      <c r="B54" t="e" cm="1">
+        <f t="array" aca="1" ref="B54" ca="1">_xll.qlStochasticProcess1DExpectation(B8,0,B20,B23)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>22</v>
       </c>
-      <c r="B55" cm="1">
-        <f t="array" ref="B55">_xll.qlStochasticProcess1DStdDeviation(B8,0,B20,B23)</f>
-        <v>28.284271247461902</v>
+      <c r="B55" t="e" cm="1">
+        <f t="array" aca="1" ref="B55" ca="1">_xll.qlStochasticProcess1DStdDeviation(B8,0,B20,B23)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>23</v>
       </c>
-      <c r="B56" cm="1">
-        <f t="array" ref="B56">_xll.qlStochasticProcess1DVariance(B8,0,B20,B23)</f>
-        <v>800</v>
+      <c r="B56" t="e" cm="1">
+        <f t="array" aca="1" ref="B56" ca="1">_xll.qlStochasticProcess1DVariance(B8,0,B20,B23)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>24</v>
       </c>
-      <c r="B57" cm="1">
+      <c r="B57" t="e" cm="1">
         <f t="array" aca="1" ref="B57" ca="1">_xll.qlStochasticProcess1DEvolve(B8,0,B20,B23,B44)</f>
-        <v>103.89912732663258</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>25</v>
       </c>
-      <c r="B58" cm="1">
-        <f t="array" ref="B58">_xll.qlStochasticProcess1DApply(B8,B20,B52)</f>
-        <v>105</v>
+      <c r="B58" t="e" cm="1">
+        <f t="array" aca="1" ref="B58" ca="1">_xll.qlStochasticProcess1DApply(B8,B20,B52)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -1291,9 +1245,9 @@
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="1" cm="1">
-        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>46174</v>
+      <c r="B2" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1327,168 +1281,168 @@
       <c r="A7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" t="str" cm="1">
-        <f t="array" ref="B7">_xll.qlFlatForward(B1,0.03)</f>
-        <v>⚡[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R7C2YieldTermStructureHandle,A</v>
+      <c r="B7" t="e" cm="1">
+        <f t="array" aca="1" ref="B7" ca="1">_xll.qlFlatForward(B1,0.03)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" t="str" cm="1">
-        <f t="array" ref="B8">_xll.qlFlatForward(B1,0.02)</f>
-        <v>⚡[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R8C2YieldTermStructureHandle,A</v>
+      <c r="B8" t="e" cm="1">
+        <f t="array" aca="1" ref="B8" ca="1">_xll.qlFlatForward(B1,0.02)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="str" cm="1">
-        <f t="array" ref="B9">_xll.qlBlackConstantVol(B2,"NullCalendar",B3,B5)</f>
-        <v>⚡[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R9C2BlackVolTermStructureHandle,A</v>
+      <c r="B9" t="e" cm="1">
+        <f t="array" aca="1" ref="B9" ca="1">_xll.qlBlackConstantVol(B2,"NullCalendar",B3,B5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B10" t="str" cm="1">
-        <f t="array" ref="B10">_xll.qlLocalConstantVol(B2,B3+0.05,B5)</f>
-        <v>⚡[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R10C2LocalVolTermStructureHandle,A</v>
+      <c r="B10" t="e" cm="1">
+        <f t="array" aca="1" ref="B10" ca="1">_xll.qlLocalConstantVol(B2,B3+0.05,B5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>31</v>
       </c>
-      <c r="B12" t="str" cm="1">
-        <f t="array" ref="B12">_xll.qlGeneralizedBlackScholesProcess(B4,B7,B8,B9)</f>
-        <v>⚡[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R12C2GeneralizedBlackScholesProcess,A</v>
+      <c r="B12" t="e" cm="1">
+        <f t="array" aca="1" ref="B12" ca="1">_xll.qlGeneralizedBlackScholesProcess(B4,B7,B8,B9)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>45</v>
       </c>
-      <c r="B13" t="str" cm="1">
-        <f t="array" ref="B13">_xll.qlGeneralizedBlackScholesProcess(B4,B7,B8,B9,B10)</f>
-        <v>⚡[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R13C2GeneralizedBlackScholesProcess,A</v>
+      <c r="B13" t="e" cm="1">
+        <f t="array" aca="1" ref="B13" ca="1">_xll.qlGeneralizedBlackScholesProcess(B4,B7,B8,B9,B10)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>32</v>
       </c>
-      <c r="B15" cm="1">
-        <f t="array" ref="B15">_xll.qlGeneralizedBlackScholesProcessStateVariable(B12)</f>
-        <v>100</v>
+      <c r="B15" t="e" cm="1">
+        <f t="array" aca="1" ref="B15" ca="1">_xll.qlGeneralizedBlackScholesProcessStateVariable(B12)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>33</v>
       </c>
-      <c r="B16" t="str" cm="1">
-        <f t="array" ref="B16">_xll.qlGeneralizedBlackScholesProcessDividendYield(B12)</f>
-        <v>⚡[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R16C2YieldTermStructureHandle,A</v>
+      <c r="B16" t="e" cm="1">
+        <f t="array" aca="1" ref="B16" ca="1">_xll.qlGeneralizedBlackScholesProcessDividendYield(B12)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>34</v>
       </c>
-      <c r="B17" t="str" cm="1">
-        <f t="array" ref="B17">_xll.qlGeneralizedBlackScholesProcessRiskFreeRate(B12)</f>
-        <v>⚡[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R17C2YieldTermStructureHandle,A</v>
+      <c r="B17" t="e" cm="1">
+        <f t="array" aca="1" ref="B17" ca="1">_xll.qlGeneralizedBlackScholesProcessRiskFreeRate(B12)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>35</v>
       </c>
-      <c r="B18" t="str" cm="1">
-        <f t="array" ref="B18">_xll.qlGeneralizedBlackScholesProcessBlackVolatility(B12)</f>
-        <v>⚡[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R18C2BlackVolTermStructureHandle,A</v>
+      <c r="B18" t="e" cm="1">
+        <f t="array" aca="1" ref="B18" ca="1">_xll.qlGeneralizedBlackScholesProcessBlackVolatility(B12)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="3" t="str" cm="1">
-        <f t="array" ref="B19">_xll.qlGeneralizedBlackScholesProcessLocalVolatility(B12)</f>
-        <v>⚡[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R19C2LocalVolTermStructureHandle,A</v>
-      </c>
-      <c r="L19" cm="1">
-        <f t="array" ref="L19">_xll.qlLocalVolTermStructureLocalVol(B19,B1+1,B4)</f>
-        <v>0.25</v>
+      <c r="B19" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="B19" ca="1">_xll.qlGeneralizedBlackScholesProcessLocalVolatility(B12)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L19" t="e" cm="1">
+        <f t="array" aca="1" ref="L19" ca="1">_xll.qlLocalVolTermStructureLocalVol(B19,B1+1,B4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="3" t="str" cm="1">
-        <f t="array" ref="B20">_xll.qlGeneralizedBlackScholesProcessLocalVolatility(B13)</f>
-        <v>⚡[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R20C2LocalVolTermStructureHandle,A</v>
-      </c>
-      <c r="L20" s="2" cm="1">
-        <f t="array" ref="L20">_xll.qlLocalVolTermStructureLocalVol(B20,B2+1,B4)</f>
-        <v>0.3</v>
+      <c r="B20" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="B20" ca="1">_xll.qlGeneralizedBlackScholesProcessLocalVolatility(B13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L20" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="L20" ca="1">_xll.qlLocalVolTermStructureLocalVol(B20,B2+1,B4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>37</v>
       </c>
-      <c r="B22" t="str" cm="1">
-        <f t="array" ref="B22">_xll.qlBlackScholesProcess(B4,B8,B9)</f>
-        <v>⚡[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R22C2BlackScholesProcess,A</v>
-      </c>
-      <c r="K22" cm="1">
-        <f t="array" ref="K22">_xll.qlStochasticProcess1DX0(B22)</f>
-        <v>100</v>
+      <c r="B22" t="e" cm="1">
+        <f t="array" aca="1" ref="B22" ca="1">_xll.qlBlackScholesProcess(B4,B8,B9)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K22" t="e" cm="1">
+        <f t="array" aca="1" ref="K22" ca="1">_xll.qlStochasticProcess1DX0(B22)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>38</v>
       </c>
-      <c r="B23" t="str" cm="1">
-        <f t="array" ref="B23">_xll.qlBlackScholesMertonProcess(B4,B7,B8,B9)</f>
-        <v>⚡[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R23C2BlackScholesMertonProcess,A</v>
-      </c>
-      <c r="K23" cm="1">
-        <f t="array" ref="K23">_xll.qlStochasticProcess1DX0(B23)</f>
-        <v>100</v>
+      <c r="B23" t="e" cm="1">
+        <f t="array" aca="1" ref="B23" ca="1">_xll.qlBlackScholesMertonProcess(B4,B7,B8,B9)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K23" t="e" cm="1">
+        <f t="array" aca="1" ref="K23" ca="1">_xll.qlStochasticProcess1DX0(B23)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>39</v>
       </c>
-      <c r="B24" t="str" cm="1">
-        <f t="array" ref="B24">_xll.qlBlackProcess(B4,B8,B9)</f>
-        <v>⚡[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R24C2BlackProcess,A</v>
-      </c>
-      <c r="K24" cm="1">
-        <f t="array" ref="K24">_xll.qlStochasticProcess1DX0(B24)</f>
-        <v>100</v>
+      <c r="B24" t="e" cm="1">
+        <f t="array" aca="1" ref="B24" ca="1">_xll.qlBlackProcess(B4,B8,B9)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K24" t="e" cm="1">
+        <f t="array" aca="1" ref="K24" ca="1">_xll.qlStochasticProcess1DX0(B24)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>40</v>
       </c>
-      <c r="B25" t="str" cm="1">
-        <f t="array" ref="B25">_xll.qlGarmanKohlagenProcess(B4,B7,B8,B9)</f>
-        <v>⚡[test_stochasticprocess.xlsx](Generalised)Black(Scholes)!R25C2GarmanKohlagenProcess,A</v>
-      </c>
-      <c r="K25" cm="1">
-        <f t="array" ref="K25">_xll.qlStochasticProcess1DX0(B25)</f>
-        <v>100</v>
+      <c r="B25" t="e" cm="1">
+        <f t="array" aca="1" ref="B25" ca="1">_xll.qlGarmanKohlagenProcess(B4,B7,B8,B9)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K25" t="e" cm="1">
+        <f t="array" aca="1" ref="K25" ca="1">_xll.qlStochasticProcess1DX0(B25)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -1517,9 +1471,9 @@
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="1" cm="1">
-        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>46174</v>
+      <c r="B2" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1534,27 +1488,27 @@
       <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="str" cm="1">
-        <f t="array" ref="B6">_xll.qlFlatForward($B$2,0.03)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R6C2YieldTermStructureHandle,A</v>
+      <c r="B6" t="e" cm="1">
+        <f t="array" aca="1" ref="B6" ca="1">_xll.qlFlatForward($B$2,0.03)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" t="str" cm="1">
-        <f t="array" ref="B7">_xll.qlFlatForward($B$2,0.02)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R7C2YieldTermStructureHandle,A</v>
+      <c r="B7" t="e" cm="1">
+        <f t="array" aca="1" ref="B7" ca="1">_xll.qlFlatForward($B$2,0.02)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>47</v>
       </c>
-      <c r="B8" t="str" cm="1">
-        <f t="array" ref="B8">_xll.qlBlackConstantVol(B2,"NullCalendar",0.25,"Act/365")</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R8C2BlackVolTermStructureHandle,A</v>
+      <c r="B8" t="e" cm="1">
+        <f t="array" aca="1" ref="B8" ca="1">_xll.qlBlackConstantVol(B2,"NullCalendar",0.25,"Act/365")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1585,18 +1539,18 @@
       <c r="A13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B13" t="str" cm="1">
-        <f t="array" ref="B13">_xll.qlMerton76Process(B5,B6,B7,B8,B10,B11,B12)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R13C2Merton76Process,A</v>
+      <c r="B13" t="e" cm="1">
+        <f t="array" aca="1" ref="B13" ca="1">_xll.qlMerton76Process(B5,B6,B7,B8,B10,B11,B12)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" cm="1">
-        <f t="array" ref="B14">_xll.qlStochasticProcessInitialValues(B13)</f>
-        <v>100</v>
+      <c r="B14" t="e" cm="1">
+        <f t="array" aca="1" ref="B14" ca="1">_xll.qlStochasticProcessInitialValues(B13)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -1630,18 +1584,18 @@
       <c r="A19" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B19" t="str" cm="1">
-        <f t="array" ref="B19">_xll.qlVarianceGammaProcess(B5,B6,B7,B16,B17,B18)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R19C2VarianceGammaProcess,A</v>
+      <c r="B19" t="e" cm="1">
+        <f t="array" aca="1" ref="B19" ca="1">_xll.qlVarianceGammaProcess(B5,B6,B7,B16,B17,B18)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>8</v>
       </c>
-      <c r="B20" cm="1">
-        <f t="array" ref="B20">_xll.qlStochasticProcessInitialValues(B19)</f>
-        <v>100</v>
+      <c r="B20" t="e" cm="1">
+        <f t="array" aca="1" ref="B20" ca="1">_xll.qlStochasticProcessInitialValues(B19)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -1696,36 +1650,36 @@
       <c r="A28" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B28" t="str" cm="1">
-        <f t="array" ref="B28">_xll.qlHestonProcess(B7,B6,B5,B22,B23,B24,B25,B26,B27)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R28C2HestonProcess,A</v>
+      <c r="B28" t="e" cm="1">
+        <f t="array" aca="1" ref="B28" ca="1">_xll.qlHestonProcess(B7,B6,B5,B22,B23,B24,B25,B26,B27)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>62</v>
       </c>
-      <c r="B29" cm="1">
-        <f t="array" ref="B29">_xll.qlHestonProcessS0(B28)</f>
-        <v>100</v>
+      <c r="B29" t="e" cm="1">
+        <f t="array" aca="1" ref="B29" ca="1">_xll.qlHestonProcessS0(B28)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>63</v>
       </c>
-      <c r="B30" t="str" cm="1">
-        <f t="array" ref="B30">_xll.qlHestonProcessRiskFreeRate(B28)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R30C2YieldTermStructureHandle,A</v>
+      <c r="B30" t="e" cm="1">
+        <f t="array" aca="1" ref="B30" ca="1">_xll.qlHestonProcessRiskFreeRate(B28)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>64</v>
       </c>
-      <c r="B31" t="str" cm="1">
-        <f t="array" ref="B31">_xll.qlHestonProcessDividendYield(B28)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R31C2YieldTermStructureHandle,A</v>
+      <c r="B31" t="e" cm="1">
+        <f t="array" aca="1" ref="B31" ca="1">_xll.qlHestonProcessDividendYield(B28)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -1820,23 +1774,18 @@
       <c r="A41" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B41" t="str" cm="1">
-        <f t="array" ref="B41">_xll.qlBatesProcess(B7,B6,B5,B33,B34,B35,B36,B37,B38,B39,B40)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R41C2BatesProcess,A</v>
+      <c r="B41" t="e" cm="1">
+        <f t="array" aca="1" ref="B41" ca="1">_xll.qlBatesProcess(B7,B6,B5,B33,B34,B35,B36,B37,B38,B39,B40)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>8</v>
       </c>
-      <c r="B42" cm="1">
-        <f t="array" ref="B42:B43">_xll.qlStochasticProcessInitialValues(B41)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B43">
-        <v>0.04</v>
+      <c r="B42" t="e" cm="1">
+        <f t="array" aca="1" ref="B42" ca="1">_xll.qlStochasticProcessInitialValues(B41)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -1859,18 +1808,18 @@
       <c r="A47" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B47" t="str" cm="1">
-        <f t="array" ref="B47">_xll.qlHullWhiteProcess(B7,B45,B46)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R47C2HullWhiteProcess,A</v>
+      <c r="B47" t="e" cm="1">
+        <f t="array" aca="1" ref="B47" ca="1">_xll.qlHullWhiteProcess(B7,B45,B46)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B49" t="str" cm="1">
-        <f t="array" ref="B49">_xll.qlHullWhiteForwardProcess(B7,B45,B46)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R49C2HullWhiteForwardProcess,A</v>
+      <c r="B49" t="e" cm="1">
+        <f t="array" aca="1" ref="B49" ca="1">_xll.qlHullWhiteForwardProcess(B7,B45,B46)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -1885,9 +1834,9 @@
       <c r="A51" t="s">
         <v>79</v>
       </c>
-      <c r="B51" t="b" cm="1">
-        <f t="array" ref="B51">_xll.qlHullWhiteForwardProcessSetForwardMeasureTime(B49,B50)</f>
-        <v>1</v>
+      <c r="B51" t="e" cm="1">
+        <f t="array" aca="1" ref="B51" ca="1">_xll.qlHullWhiteForwardProcessSetForwardMeasureTime(B49,B50)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -1910,27 +1859,27 @@
       <c r="A54" t="s">
         <v>82</v>
       </c>
-      <c r="B54" cm="1">
-        <f t="array" ref="B54">_xll.qlHullWhiteForwardProcessAlpha(B49,B53)</f>
-        <v>2.0761142093436498E-2</v>
+      <c r="B54" t="e" cm="1">
+        <f t="array" aca="1" ref="B54" ca="1">_xll.qlHullWhiteForwardProcessAlpha(B49,B53)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>83</v>
       </c>
-      <c r="B55" cm="1">
-        <f t="array" ref="B55">_xll.qlHullWhiteForwardProcessB(B49,B52,B53)</f>
-        <v>2.9554466451491845</v>
+      <c r="B55" t="e" cm="1">
+        <f t="array" aca="1" ref="B55" ca="1">_xll.qlHullWhiteForwardProcessB(B49,B52,B53)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>84</v>
       </c>
-      <c r="B56" cm="1">
-        <f t="array" ref="B56">_xll.qlHullWhiteForwardProcessMT(B49,B52,B53,B53)</f>
-        <v>2.7950927591437191E-4</v>
+      <c r="B56" t="e" cm="1">
+        <f t="array" aca="1" ref="B56" ca="1">_xll.qlHullWhiteForwardProcessMT(B49,B52,B53,B53)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -1977,18 +1926,18 @@
       <c r="A63" t="s">
         <v>88</v>
       </c>
-      <c r="B63" t="str" cm="1">
-        <f t="array" ref="B63">_xll.qlG2Process(B58,B59,B60,B61,B62)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R63C2G2Process,A</v>
+      <c r="B63" t="e" cm="1">
+        <f t="array" aca="1" ref="B63" ca="1">_xll.qlG2Process(B58,B59,B60,B61,B62)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>90</v>
       </c>
-      <c r="B65" t="str" cm="1">
-        <f t="array" ref="B65">_xll.qlG2ForwardProcess(B58,B59,B60,B61,B62)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R65C2G2ForwardProcess,A</v>
+      <c r="B65" t="e" cm="1">
+        <f t="array" aca="1" ref="B65" ca="1">_xll.qlG2ForwardProcess(B58,B59,B60,B61,B62)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -2003,9 +1952,9 @@
       <c r="A67" t="s">
         <v>91</v>
       </c>
-      <c r="B67" t="b" cm="1">
-        <f t="array" ref="B67">_xll.qlG2ForwardProcessSetForwardMeasureTime(B65,B66)</f>
-        <v>1</v>
+      <c r="B67" t="e" cm="1">
+        <f t="array" aca="1" ref="B67" ca="1">_xll.qlG2ForwardProcessSetForwardMeasureTime(B65,B66)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -2060,9 +2009,9 @@
       <c r="A73" t="s">
         <v>95</v>
       </c>
-      <c r="B73" t="str" cm="1">
-        <f t="array" ref="B73">_xll.qlGsrProcess(B70:D70,B71:E71,B72:E72)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R73C2GsrProcess,A</v>
+      <c r="B73" t="e" cm="1">
+        <f t="array" aca="1" ref="B73" ca="1">_xll.qlGsrProcess(B70:D70,B71:E71,B72:E72)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -2074,14 +2023,9 @@
       <c r="A75" t="s">
         <v>101</v>
       </c>
-      <c r="B75" t="str" cm="1">
-        <f t="array" ref="B75">_xll.qlGsrProcessSigma(B73,4)</f>
-        <v xml:space="preserve">NotImplementedError: NotImplementedError: qlGsrProcessSigma is currently broken.
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlib_xloil\stochasticprocess.py", line 839, in qlGsrProcessSigma
-    raise NotImplementedError("qlGsrProcessSigma is currently broken.")
-NotImplementedError: qlGsrProcessSigma is currently broken.
-</v>
+      <c r="B75" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="B75" ca="1">FIND("NotImplementedError: NotImplementedError: qlGsrProcessSigma is currently broken", _xll.qlGsrProcessSigma(B73,4))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -2120,36 +2064,36 @@
       <c r="A82" t="s">
         <v>102</v>
       </c>
-      <c r="B82" t="str" cm="1">
-        <f t="array" ref="B82">_xll.qlOrnsteinUhlenbeckProcess(B78,B79,B80,B81)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R82C2OrnsteinUhlenbeckProcess,A</v>
+      <c r="B82" t="e" cm="1">
+        <f t="array" aca="1" ref="B82" ca="1">_xll.qlOrnsteinUhlenbeckProcess(B78,B79,B80,B81)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>103</v>
       </c>
-      <c r="B83" cm="1">
-        <f t="array" ref="B83">_xll.qlOrnsteinUhlenbeckProcessSpeed(B82)</f>
-        <v>0.1</v>
+      <c r="B83" t="e" cm="1">
+        <f t="array" aca="1" ref="B83" ca="1">_xll.qlOrnsteinUhlenbeckProcessSpeed(B82)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>104</v>
       </c>
-      <c r="B84" cm="1">
-        <f t="array" ref="B84">_xll.qlOrnsteinUhlenbeckProcessVolatility(B82)</f>
-        <v>0.01</v>
+      <c r="B84" t="e" cm="1">
+        <f t="array" aca="1" ref="B84" ca="1">_xll.qlOrnsteinUhlenbeckProcessVolatility(B82)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>105</v>
       </c>
-      <c r="B85" cm="1">
-        <f t="array" ref="B85">_xll.qlOrnsteinUhlenbeckProcessLevel(B82)</f>
-        <v>0.04</v>
+      <c r="B85" t="e" cm="1">
+        <f t="array" aca="1" ref="B85" ca="1">_xll.qlOrnsteinUhlenbeckProcessLevel(B82)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -2172,18 +2116,18 @@
       <c r="A89" t="s">
         <v>107</v>
       </c>
-      <c r="B89" t="str" cm="1">
-        <f t="array" ref="B89">_xll.qlExtendedOrnsteinUhlenbeckProcessConstantFunction(B87)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R88C2function,A</v>
+      <c r="B89" t="e" cm="1">
+        <f t="array" aca="1" ref="B89" ca="1">_xll.qlExtendedOrnsteinUhlenbeckProcessConstantFunction(B87)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>109</v>
       </c>
-      <c r="B90" t="str" cm="1">
-        <f t="array" ref="B90">_xll.qlExtendedOrnsteinUhlenbeckProcess(B78,B79,B80,B89,B88)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R90C2ExtendedOrnsteinUhlenbeckProcess,A</v>
+      <c r="B90" t="e" cm="1">
+        <f t="array" aca="1" ref="B90" ca="1">_xll.qlExtendedOrnsteinUhlenbeckProcess(B78,B79,B80,B89,B88)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
@@ -2222,9 +2166,9 @@
       <c r="A96" t="s">
         <v>113</v>
       </c>
-      <c r="B96" t="str" cm="1">
-        <f t="array" ref="B96">_xll.qlExtOUWithJumpsProcess(B90,B92,B93,B94,B95)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R96C2ExtOUWithJumpsProcess,A</v>
+      <c r="B96" t="e" cm="1">
+        <f t="array" aca="1" ref="B96" ca="1">_xll.qlExtOUWithJumpsProcess(B90,B92,B93,B94,B95)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
@@ -2239,24 +2183,18 @@
       <c r="A99" t="s">
         <v>114</v>
       </c>
-      <c r="B99" t="str" cm="1">
-        <f t="array" ref="B99">_xll.qlKlugeExtOUProcess(B98,B96,B90)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R99C2KlugeExtOUProcess,A</v>
+      <c r="B99" t="e" cm="1">
+        <f t="array" aca="1" ref="B99" ca="1">_xll.qlKlugeExtOUProcess(B98,B96,B90)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>8</v>
       </c>
-      <c r="B100" cm="1">
-        <f t="array" ref="B100:D100">TRANSPOSE(_xll.qlStochasticProcessInitialValues(B99))</f>
-        <v>0.03</v>
-      </c>
-      <c r="C100">
-        <v>1</v>
-      </c>
-      <c r="D100">
-        <v>0.03</v>
+      <c r="B100" t="e" cm="1">
+        <f t="array" aca="1" ref="B100" ca="1">TRANSPOSE(_xll.qlStochasticProcessInitialValues(B99))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -2369,36 +2307,36 @@
       <c r="A111" t="s">
         <v>131</v>
       </c>
-      <c r="B111" t="str" cm="1">
-        <f t="array" ref="B111">_xll.qlGJRGARCHProcess(B7,B6,B5,B103,B104,B105,B106,B107,B108,B109,B110)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R111C2GJRGARCHProcess,A</v>
+      <c r="B111" t="e" cm="1">
+        <f t="array" aca="1" ref="B111" ca="1">_xll.qlGJRGARCHProcess(B7,B6,B5,B103,B104,B105,B106,B107,B108,B109,B110)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>132</v>
       </c>
-      <c r="B112" cm="1">
-        <f t="array" ref="B112">_xll.qlGJRGARCHProcessS0(B111)</f>
-        <v>100</v>
+      <c r="B112" t="e" cm="1">
+        <f t="array" aca="1" ref="B112" ca="1">_xll.qlGJRGARCHProcessS0(B111)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>133</v>
       </c>
-      <c r="B113" t="str" cm="1">
-        <f t="array" ref="B113">_xll.qlGJRGARCHProcessRiskFreeRate(B111)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R113C2YieldTermStructureHandle,A</v>
+      <c r="B113" t="e" cm="1">
+        <f t="array" aca="1" ref="B113" ca="1">_xll.qlGJRGARCHProcessRiskFreeRate(B111)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>134</v>
       </c>
-      <c r="B114" t="str" cm="1">
-        <f t="array" ref="B114">_xll.qlGJRGARCHProcessDividendYield(B111)</f>
-        <v>⚡[test_stochasticprocess.xlsx]StochasticProcesses!R114C2YieldTermStructureHandle,A</v>
+      <c r="B114" t="e" cm="1">
+        <f t="array" aca="1" ref="B114" ca="1">_xll.qlGJRGARCHProcessDividendYield(B111)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
